--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.7</t>
+          <t>globalid-disease-ontology:2026.08.8</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.8</t>
+          <t>globalid-disease-ontology:2026.08.10</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.10</t>
+          <t>globalid-disease-ontology:2026.08.28</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28</t>
+          <t>globalid-disease-ontology:2026.08.28.1</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.1</t>
+          <t>globalid-disease-ontology:2026.08.28.2</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">

--- a/countries/ch/2010-2014.xlsx
+++ b/countries/ch/2010-2014.xlsx
@@ -1152,7 +1152,7 @@
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
@@ -6742,7 +6742,7 @@
       </c>
       <c r="AJ41" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK41" t="inlineStr">
@@ -9506,7 +9506,7 @@
       </c>
       <c r="AJ59" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK59" t="inlineStr">
@@ -12270,7 +12270,7 @@
       </c>
       <c r="AJ77" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK77" t="inlineStr">
@@ -15182,7 +15182,7 @@
       </c>
       <c r="AJ96" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK96" t="inlineStr">
@@ -17946,7 +17946,7 @@
       </c>
       <c r="AJ114" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK114" t="inlineStr">
@@ -20710,7 +20710,7 @@
       </c>
       <c r="AJ132" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK132" t="inlineStr">
@@ -23622,7 +23622,7 @@
       </c>
       <c r="AJ151" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK151" t="inlineStr">
@@ -26386,7 +26386,7 @@
       </c>
       <c r="AJ169" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK169" t="inlineStr">
@@ -29150,7 +29150,7 @@
       </c>
       <c r="AJ187" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK187" t="inlineStr">
@@ -32062,7 +32062,7 @@
       </c>
       <c r="AJ206" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK206" t="inlineStr">
@@ -34826,7 +34826,7 @@
       </c>
       <c r="AJ224" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK224" t="inlineStr">
@@ -37590,7 +37590,7 @@
       </c>
       <c r="AJ242" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK242" t="inlineStr">
@@ -39022,7 +39022,7 @@
       </c>
       <c r="AJ251" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK251" t="inlineStr">
@@ -44612,7 +44612,7 @@
       </c>
       <c r="AJ288" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK288" t="inlineStr">
@@ -47376,7 +47376,7 @@
       </c>
       <c r="AJ306" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK306" t="inlineStr">
@@ -50140,7 +50140,7 @@
       </c>
       <c r="AJ324" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK324" t="inlineStr">
@@ -53052,7 +53052,7 @@
       </c>
       <c r="AJ343" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK343" t="inlineStr">
@@ -55816,7 +55816,7 @@
       </c>
       <c r="AJ361" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK361" t="inlineStr">
@@ -58580,7 +58580,7 @@
       </c>
       <c r="AJ379" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK379" t="inlineStr">
@@ -61492,7 +61492,7 @@
       </c>
       <c r="AJ398" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK398" t="inlineStr">
@@ -64256,7 +64256,7 @@
       </c>
       <c r="AJ416" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK416" t="inlineStr">
@@ -67168,7 +67168,7 @@
       </c>
       <c r="AJ435" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK435" t="inlineStr">
@@ -69932,7 +69932,7 @@
       </c>
       <c r="AJ453" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK453" t="inlineStr">
@@ -72696,7 +72696,7 @@
       </c>
       <c r="AJ471" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK471" t="inlineStr">
@@ -75608,7 +75608,7 @@
       </c>
       <c r="AJ490" t="inlineStr">
         <is>
-          <t>globalid-disease-ontology:2026.08.28.2</t>
+          <t>globalid-disease-ontology:2026.08.30.1</t>
         </is>
       </c>
       <c r="AK490" t="inlineStr">
